--- a/data/trans_bre/P1418-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1418-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,84</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,34</t>
+          <t>1,19; 9,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 9,39</t>
+          <t>1,55; 9,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 12,22</t>
+          <t>4,72; 12,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,77</t>
+          <t>-0,95; 2,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 361,76</t>
+          <t>15,56; 359,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,07; 511,12</t>
+          <t>24,9; 468,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>125,33; 1290,56</t>
+          <t>133,81; 1400,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 330,81</t>
+          <t>-42,15; 303,13</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>154,88%</t>
+          <t>147,69%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,58</t>
+          <t>3,76; 11,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,21</t>
+          <t>1,34; 7,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,6</t>
+          <t>0,93; 5,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,64</t>
+          <t>1,38; 5,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>48,47; 274,15</t>
+          <t>49,66; 273,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,63; 459,83</t>
+          <t>21,02; 470,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,51; 544,02</t>
+          <t>27,05; 544,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,26; 420,14</t>
+          <t>22,18; 390,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,94</t>
+          <t>0,56; 7,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,77</t>
+          <t>-0,06; 6,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 3,73</t>
+          <t>-1,94; 3,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,03</t>
+          <t>-1,02; 5,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 290,91</t>
+          <t>3,73; 312,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 338,28</t>
+          <t>-10,55; 314,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,62; 177,24</t>
+          <t>-46,35; 187,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 119,93</t>
+          <t>-13,35; 121,03</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,72</t>
+          <t>1,69; 7,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 14,57</t>
+          <t>6,13; 14,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 5,94</t>
+          <t>0,12; 5,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,05</t>
+          <t>-1,66; 3,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,51; 361,8</t>
+          <t>33,41; 375,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>113,16; 570,23</t>
+          <t>99,2; 537,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 538,82</t>
+          <t>-9,68; 436,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 115,71</t>
+          <t>-29,0; 149,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,48</t>
+          <t>7,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>234,99%</t>
+          <t>265,46%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 11,24</t>
+          <t>0,39; 10,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 16,28</t>
+          <t>5,37; 16,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 10,21</t>
+          <t>2,93; 9,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 10,97</t>
+          <t>4,44; 10,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 347,52</t>
+          <t>-2,49; 346,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,72; 544,34</t>
+          <t>56,4; 586,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>80,65; 564,16</t>
+          <t>91,21; 619,7</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 10,92</t>
+          <t>2,56; 11,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 10,59</t>
+          <t>2,31; 10,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,03</t>
+          <t>-0,48; 6,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 10,66</t>
+          <t>2,53; 10,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,96; 479,71</t>
+          <t>35,33; 503,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,29; 590,38</t>
+          <t>34,27; 526,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 352,31</t>
+          <t>-14,44; 380,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,18; 155,68</t>
+          <t>23,81; 160,47</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>154,07%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,87</t>
+          <t>1,26; 7,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,48</t>
+          <t>4,07; 10,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,99</t>
+          <t>4,44; 9,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 11,4</t>
+          <t>6,95; 12,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,43; 192,34</t>
+          <t>20,9; 200,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,23; 356,55</t>
+          <t>70,08; 336,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,57; 430,44</t>
+          <t>101,95; 436,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 201,39</t>
+          <t>85,33; 256,23</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>189,33%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 5,64</t>
+          <t>-0,65; 5,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,09</t>
+          <t>4,81; 9,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,81</t>
+          <t>3,35; 7,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,14</t>
+          <t>1,11; 4,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 76,6</t>
+          <t>-5,39; 73,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>228,1; 1237,4</t>
+          <t>219,01; 1250,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>107,85; 538,87</t>
+          <t>104,61; 514,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>67,46; 550,15</t>
+          <t>24,37; 217,82</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,59</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>106,08%</t>
+          <t>108,22%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,01</t>
+          <t>3,4; 5,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,86</t>
+          <t>5,41; 7,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,71; 5,85</t>
+          <t>3,69; 5,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,57</t>
+          <t>3,57; 5,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>56,66; 125,54</t>
+          <t>56,74; 121,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>147,61; 293,13</t>
+          <t>150,65; 288,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>129,05; 276,79</t>
+          <t>131,9; 283,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>64,14; 160,16</t>
+          <t>75,24; 146,91</t>
         </is>
       </c>
     </row>
